--- a/data/trans_orig/IP07A16-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07A16-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de ayudarse entre los amigos en 2007 (tasa de respuesta: 99,2%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2007 (tasa de respuesta: 99,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12712</t>
+          <t>11947</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9173</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19498</t>
+          <t>20348</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12394</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15717</t>
+          <t>15928</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14326</t>
+          <t>14557</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25798</t>
+          <t>25659</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,33%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9743</t>
+          <t>9839</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7499</t>
+          <t>7529</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16017</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23582</t>
+          <t>23571</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,4%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25102</t>
+          <t>25311</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34707</t>
+          <t>34598</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46482</t>
+          <t>45918</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53884</t>
+          <t>53891</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74242</t>
+          <t>74268</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86900</t>
+          <t>86923</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,2%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>17141</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11195</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>23280</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23317</t>
+          <t>23346</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16408</t>
+          <t>16003</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23688</t>
+          <t>24227</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36899</t>
+          <t>37339</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>57,07%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9342</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19140</t>
+          <t>18580</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>12273</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20524</t>
+          <t>20466</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23520</t>
+          <t>23677</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37134</t>
+          <t>36527</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>55,83%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>792</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>10961</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21210</t>
+          <t>21109</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20751</t>
+          <t>20277</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23682</t>
+          <t>23693</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37622</t>
+          <t>37774</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,62%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14086</t>
+          <t>13669</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24833</t>
+          <t>23810</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15893</t>
+          <t>15854</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26170</t>
+          <t>26321</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>33315</t>
+          <t>33865</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48393</t>
+          <t>47986</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>61,76%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>593</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10842</t>
+          <t>11520</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>15826</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>12010</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15700</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>26303</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,12%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7754</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16087</t>
+          <t>15448</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20510</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,59%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7368</t>
+          <t>7393</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>710</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10819</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>11496</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>19987</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>7872</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>16641</t>
+          <t>16031</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>21806</t>
+          <t>21720</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>33875</t>
+          <t>33994</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,51%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13514</t>
+          <t>13525</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11378</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20284</t>
+          <t>19791</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>19108</t>
+          <t>19644</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>31619</t>
+          <t>31646</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,47%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6125</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9733</t>
+          <t>9459</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>24224</t>
+          <t>24983</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>36341</t>
+          <t>36521</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,82 +4839,82 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
+          <t>44,04%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>64,38%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>28978</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>22469</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>35250</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>46,96%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>36,41%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>57,12%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>59670</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>50575</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>68794</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>50,38%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
           <t>42,7%</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>64,06%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>28978</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>22762</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>34978</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>46,96%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>36,89%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>56,68%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>59670</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>50815</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>69151</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>50,38%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>42,9%</t>
-        </is>
-      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,08%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>14762</t>
+          <t>14548</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26508</t>
+          <t>25875</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>21781</t>
+          <t>21837</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>33704</t>
+          <t>34299</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>38931</t>
+          <t>38669</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>57182</t>
+          <t>56386</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,61%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9279</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>9992</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>15781</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>18701</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>31157</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>24242</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>37939</t>
+          <t>37703</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>45850</t>
+          <t>45987</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>64316</t>
+          <t>64861</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>32553</t>
+          <t>32222</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>45951</t>
+          <t>46367</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>29514</t>
+          <t>29186</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>43112</t>
+          <t>42824</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>65917</t>
+          <t>66562</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>85456</t>
+          <t>85753</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>5964</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>15632</t>
+          <t>16054</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>9793</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>10562</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>21963</t>
+          <t>22194</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>141217</t>
+          <t>141130</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>170193</t>
+          <t>170443</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>151318</t>
+          <t>150567</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>179244</t>
+          <t>180296</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>298967</t>
+          <t>299590</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>342634</t>
+          <t>341172</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,4%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>111637</t>
+          <t>111218</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>139724</t>
+          <t>139471</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>131597</t>
+          <t>129794</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>159695</t>
+          <t>159506</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>248607</t>
+          <t>250093</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>292369</t>
+          <t>292935</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,13%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>27038</t>
+          <t>27152</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>46715</t>
+          <t>45400</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>24157</t>
+          <t>24018</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>42223</t>
+          <t>40815</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>56279</t>
+          <t>56509</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>80962</t>
+          <t>81764</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>2446</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de ayudarse entre los amigos en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13634</t>
+          <t>14055</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20273</t>
+          <t>20551</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12789</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21871</t>
+          <t>21776</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28291</t>
+          <t>29322</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40502</t>
+          <t>41010</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,88%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>11813</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16856</t>
+          <t>17380</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>10454</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>533</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29959</t>
+          <t>30637</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39688</t>
+          <t>40190</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35620</t>
+          <t>35962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45628</t>
+          <t>46006</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68980</t>
+          <t>69193</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83323</t>
+          <t>83305</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,6%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>14425</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4337</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13087</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11298</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23860</t>
+          <t>24637</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7326</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4926</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13964</t>
+          <t>13172</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21249</t>
+          <t>21212</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21742</t>
+          <t>22656</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28491</t>
+          <t>29339</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40728</t>
+          <t>41411</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>73,1%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>10682</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>6701</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15602</t>
+          <t>15572</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>11416</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23424</t>
+          <t>23114</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>40,8%</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10332</t>
+          <t>9954</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20267</t>
+          <t>19898</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24013</t>
+          <t>23813</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25841</t>
+          <t>26853</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40591</t>
+          <t>41991</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>57,55%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15894</t>
+          <t>16495</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26091</t>
+          <t>26683</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9181</t>
+          <t>9730</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19530</t>
+          <t>19480</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28843</t>
+          <t>27925</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>43685</t>
+          <t>42695</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>58,51%</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>577</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9275</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14546</t>
+          <t>14561</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11494</t>
+          <t>11147</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21743</t>
+          <t>21508</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>51,93%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>14563</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11027</t>
+          <t>10891</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>12679</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>23043</t>
+          <t>22744</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>54,92%</t>
         </is>
       </c>
     </row>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>755</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10075,12 +10075,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>10445</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>12323</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21374</t>
+          <t>21300</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9016</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>16897</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>24076</t>
+          <t>23132</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>36081</t>
+          <t>35035</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>63,34%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14581</t>
+          <t>15507</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16042</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16638</t>
+          <t>17116</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>29019</t>
+          <t>28706</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>51,9%</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>5455</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>473</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>22523</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>35497</t>
+          <t>35326</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>24192</t>
+          <t>24439</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>36615</t>
+          <t>36669</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>50401</t>
+          <t>50725</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>67612</t>
+          <t>67686</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,44%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>17738</t>
+          <t>18061</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>30398</t>
+          <t>30171</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>29026</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>39041</t>
+          <t>38936</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>55537</t>
+          <t>55388</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,46%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7118</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>9705</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>17783</t>
+          <t>17970</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>31447</t>
+          <t>31028</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>18939</t>
+          <t>18933</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>32324</t>
+          <t>32845</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>40245</t>
+          <t>39858</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>59053</t>
+          <t>59555</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>37705</t>
+          <t>38477</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>52771</t>
+          <t>52199</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>32615</t>
+          <t>31845</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>46238</t>
+          <t>46073</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>74609</t>
+          <t>74545</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>94614</t>
+          <t>94550</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,41%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>11990</t>
+          <t>11656</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>7959</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>18148</t>
+          <t>17842</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>13407</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>26509</t>
+          <t>27155</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -12219,12 +12219,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>10142</t>
+          <t>9935</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -12337,7 +12337,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>145184</t>
+          <t>145896</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>174149</t>
+          <t>175147</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>161335</t>
+          <t>161566</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>190649</t>
+          <t>190103</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>315991</t>
+          <t>314271</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>358765</t>
+          <t>359237</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,07%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>116830</t>
+          <t>117363</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>146290</t>
+          <t>145733</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>107860</t>
+          <t>107595</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>135649</t>
+          <t>135452</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>233344</t>
+          <t>233393</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>274072</t>
+          <t>274732</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>28708</t>
+          <t>28683</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>20542</t>
+          <t>20927</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>37259</t>
+          <t>37183</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>39665</t>
+          <t>38062</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>61503</t>
+          <t>60435</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>9368</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>9171</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>14514</t>
+          <t>15202</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -13014,12 +13014,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>8832</t>
+          <t>8708</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>10680</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13099,7 +13099,7 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de ayudarse entre los amigos en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14966</t>
+          <t>14376</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23571</t>
+          <t>23329</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8113</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16981</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24560</t>
+          <t>25587</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37260</t>
+          <t>37770</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>65,3%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11474</t>
+          <t>11251</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16690</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13307</t>
+          <t>13311</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25457</t>
+          <t>25632</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,32%</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13706,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>979</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7371</t>
+          <t>7852</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11164</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27846</t>
+          <t>27272</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39351</t>
+          <t>39141</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34549</t>
+          <t>33578</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45937</t>
+          <t>45658</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65961</t>
+          <t>65753</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83180</t>
+          <t>81914</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>74,36%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19594</t>
+          <t>19842</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11342</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22715</t>
+          <t>23638</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23169</t>
+          <t>22806</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39126</t>
+          <t>38696</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -14388,12 +14388,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14403,12 +14403,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9352</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14473,12 +14473,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14521,7 +14521,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16742</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27056</t>
+          <t>27392</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21340</t>
+          <t>21797</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31281</t>
+          <t>31968</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45496</t>
+          <t>46511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>66,86%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6344</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16054</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16266</t>
+          <t>16456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30229</t>
+          <t>29848</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>42,91%</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15120,12 +15120,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13530</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,0%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23543</t>
+          <t>23073</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32173</t>
+          <t>32031</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28498</t>
+          <t>27999</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37878</t>
+          <t>37448</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54529</t>
+          <t>54167</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67410</t>
+          <t>67218</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,15%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11044</t>
+          <t>11446</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11731</t>
+          <t>12677</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20655</t>
+          <t>20917</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -15752,12 +15752,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>760</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15767,12 +15767,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7670</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15900,12 +15900,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15915,12 +15915,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15935,12 +15935,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>761</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15950,12 +15950,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13658</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7286</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8947</t>
+          <t>8754</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18739</t>
+          <t>19065</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11914</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16973</t>
+          <t>17178</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23620</t>
+          <t>23752</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>23358</t>
+          <t>23505</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>34082</t>
+          <t>33810</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>74,53%</t>
         </is>
       </c>
     </row>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>625</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>19194</t>
+          <t>19227</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26798</t>
+          <t>27174</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>20581</t>
+          <t>20305</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>28151</t>
+          <t>27726</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>42374</t>
+          <t>42382</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>53250</t>
+          <t>53227</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,68%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>846</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>14621</t>
+          <t>14842</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17397,7 +17397,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>23238</t>
+          <t>23738</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>36192</t>
+          <t>36669</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>37933</t>
+          <t>37041</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>51846</t>
+          <t>50276</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>70863</t>
+          <t>70442</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,55%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>21072</t>
+          <t>21328</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>34134</t>
+          <t>33783</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>20950</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>33162</t>
+          <t>34837</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>44715</t>
+          <t>45426</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>63652</t>
+          <t>64680</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>15534</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10675</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>10573</t>
+          <t>10740</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>23522</t>
+          <t>22973</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -17916,7 +17916,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17931,7 +17931,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>27736</t>
+          <t>27672</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>41575</t>
+          <t>41560</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>32057</t>
+          <t>33160</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>46327</t>
+          <t>47885</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>64686</t>
+          <t>65601</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>85135</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,94%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>28508</t>
+          <t>28960</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>43273</t>
+          <t>42821</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>22083</t>
+          <t>21816</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>35725</t>
+          <t>35743</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>54218</t>
+          <t>53833</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>74112</t>
+          <t>73773</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,21%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>13411</t>
+          <t>13432</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11578</t>
+          <t>12120</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>22473</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -18598,7 +18598,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18633,7 +18633,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18668,7 +18668,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -18781,7 +18781,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>186121</t>
+          <t>187710</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>217365</t>
+          <t>216261</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>186005</t>
+          <t>185946</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>218520</t>
+          <t>217062</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>380451</t>
+          <t>382305</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>424121</t>
+          <t>425804</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,64%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>100722</t>
+          <t>100133</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>129039</t>
+          <t>129206</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>111992</t>
+          <t>111627</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>142218</t>
+          <t>142207</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>221450</t>
+          <t>220659</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>262250</t>
+          <t>263300</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>23663</t>
+          <t>23680</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>41923</t>
+          <t>42420</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>18224</t>
+          <t>18563</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>34803</t>
+          <t>35150</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>46788</t>
+          <t>47572</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>70583</t>
+          <t>72876</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19290,12 +19290,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19330,7 +19330,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>15434</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -19393,7 +19393,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19478,7 +19478,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
